--- a/catalogo_old.xlsx
+++ b/catalogo_old.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="853">
   <si>
     <t xml:space="preserve">Nombre del producto</t>
   </si>
@@ -1030,10 +1030,7 @@
     <t xml:space="preserve">img-0048.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Ácido Hialurónico - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5%; Vitamina E; D-Panthenol; Filtros Solares Químicos y Minerales</t>
+    <t xml:space="preserve">Ácido Hialurónico – 1 5%; Vitamina E; D-Panthenol; Filtros Solares Químicos y Minerales</t>
   </si>
   <si>
     <t xml:space="preserve">Brucen Pantalla Solar Corporal SPF 50</t>
@@ -1897,9 +1894,6 @@
     <t xml:space="preserve">Bicarbonato</t>
   </si>
   <si>
-    <t xml:space="preserve">Solución Limpiadora para Manos y Cuerpo</t>
-  </si>
-  <si>
     <t xml:space="preserve">DB-COR-044</t>
   </si>
   <si>
@@ -1991,9 +1985,6 @@
   </si>
   <si>
     <t xml:space="preserve">img-0100.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solución Limpiadora para la Piel Baby</t>
   </si>
   <si>
     <t xml:space="preserve">DB-INF-001</t>
@@ -2602,6 +2593,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2619,12 +2611,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF6D"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2661,8 +2659,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2675,6 +2681,83 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF6D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF6D"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2686,37 +2769,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2789,3747 +2872,3687 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I136"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="123.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="296.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="115.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="56.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="123.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="296.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="94.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="0" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="0" t="s">
+      <c r="E6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="0" t="s">
+      <c r="E7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="0" t="s">
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="0" t="s">
+      <c r="E9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="0" t="s">
+      <c r="E10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="0" t="s">
+      <c r="E11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="E12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="0" t="s">
+      <c r="I12" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="0" t="s">
+      <c r="E13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="0" t="s">
+      <c r="I13" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="0" t="s">
+      <c r="E14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="0" t="s">
+      <c r="H14" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="0" t="s">
+      <c r="I14" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="0" t="s">
+      <c r="E15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="0" t="s">
+      <c r="H15" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="0" t="s">
+      <c r="I15" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="0" t="s">
+      <c r="E16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H16" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="0" t="s">
+      <c r="I16" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="0" t="s">
+      <c r="E17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I17" s="0" t="s">
+      <c r="I17" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="0" t="s">
+      <c r="E18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H18" s="0" t="s">
+      <c r="H18" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I18" s="0" t="s">
+      <c r="I18" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="0" t="s">
+      <c r="E19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H19" s="0" t="s">
+      <c r="H19" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I19" s="0" t="s">
+      <c r="I19" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E20" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="0" t="s">
+      <c r="E20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="0" t="s">
+      <c r="H20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I20" s="0" t="s">
+      <c r="I20" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E21" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="0" t="s">
+      <c r="E21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H21" s="0" t="s">
+      <c r="H21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I21" s="0" t="s">
+      <c r="I21" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="0" t="s">
+      <c r="E22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="0" t="s">
+      <c r="H22" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I22" s="0" t="s">
+      <c r="I22" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="0" t="s">
+      <c r="E23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I23" s="0" t="s">
+      <c r="I23" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E24" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="0" t="s">
+      <c r="E24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="H24" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I24" s="0" t="s">
+      <c r="I24" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="0" t="s">
+      <c r="E25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="H25" s="0" t="s">
+      <c r="H25" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I25" s="0" t="s">
+      <c r="I25" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="0" t="s">
+      <c r="E26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H26" s="0" t="s">
+      <c r="H26" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="0" t="s">
+      <c r="I26" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E27" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="0" t="s">
+      <c r="E27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="G27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="H27" s="0" t="s">
+      <c r="H27" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="I27" s="0" t="s">
+      <c r="I27" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E28" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="0" t="s">
+      <c r="E28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="G28" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H28" s="0" t="s">
+      <c r="H28" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I28" s="0" t="s">
+      <c r="I28" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E29" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="0" t="s">
+      <c r="E29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="H29" s="0" t="s">
+      <c r="H29" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I29" s="0" t="s">
+      <c r="I29" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E30" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="0" t="s">
+      <c r="E30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="G30" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="0" t="s">
+      <c r="H30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I30" s="0" t="s">
+      <c r="I30" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="0" t="s">
+      <c r="E31" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="G31" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="H31" s="0" t="s">
+      <c r="H31" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I31" s="0" t="s">
+      <c r="I31" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E32" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="0" t="s">
+      <c r="E32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="G32" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H32" s="0" t="s">
+      <c r="H32" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I32" s="0" t="s">
+      <c r="I32" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E33" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="0" t="s">
+      <c r="E33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H33" s="0" t="s">
+      <c r="H33" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I33" s="0" t="s">
+      <c r="I33" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E34" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="0" t="s">
+      <c r="E34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H34" s="0" t="s">
+      <c r="H34" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I34" s="0" t="s">
+      <c r="I34" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E35" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="0" t="s">
+      <c r="E35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="H35" s="0" t="s">
+      <c r="H35" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="I35" s="0" t="s">
+      <c r="I35" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E36" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="0" t="s">
+      <c r="E36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="I36" s="0" t="s">
+      <c r="I36" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E37" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" s="0" t="s">
+      <c r="E37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I37" s="0" t="s">
+      <c r="I37" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E38" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="0" t="s">
+      <c r="E38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I38" s="0" t="s">
+      <c r="I38" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E39" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="0" t="s">
+      <c r="E39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="0" t="s">
+      <c r="I39" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E40" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="0" t="s">
+      <c r="E40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I40" s="0" t="s">
+      <c r="I40" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E41" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="0" t="s">
+      <c r="E41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="G41" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="H41" s="0" t="s">
+      <c r="H41" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I41" s="0" t="s">
+      <c r="I41" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E42" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="0" t="s">
+      <c r="E42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="H42" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="I42" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E43" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="0" t="s">
+      <c r="E43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H43" s="0" t="s">
+      <c r="H43" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I43" s="0" t="s">
+      <c r="I43" s="1" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E44" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="0" t="s">
+      <c r="E44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="H44" s="0" t="s">
+      <c r="H44" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="I44" s="0" t="s">
+      <c r="I44" s="1" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E45" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="0" t="s">
+      <c r="E45" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="H45" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="I45" s="0" t="s">
+      <c r="I45" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E46" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="0" t="s">
+      <c r="E46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="H46" s="0" t="s">
+      <c r="H46" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="I46" s="0" t="s">
+      <c r="I46" s="1" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E47" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="0" t="s">
+      <c r="E47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="H47" s="0" t="s">
+      <c r="H47" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I47" s="0" t="s">
+      <c r="I47" s="1" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E48" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="0" t="s">
+      <c r="E48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="I48" s="0" t="s">
+      <c r="I48" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E49" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="0" t="s">
+      <c r="E49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="I49" s="0" t="s">
+      <c r="I49" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J49" s="0" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="C50" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="D50" s="0" t="s">
+      <c r="E50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E50" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" s="0" t="s">
+      <c r="G50" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="I50" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="I50" s="0" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="E51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" s="0" t="s">
+      <c r="G51" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="H51" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="H51" s="0" t="s">
+      <c r="I51" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I51" s="0" t="s">
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="C52" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="D52" s="0" t="s">
+      <c r="E52" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E52" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="0" t="s">
+      <c r="G52" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="H52" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="H52" s="0" t="s">
+      <c r="B53" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I52" s="0" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>357</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="D53" s="0" t="s">
-        <v>358</v>
-      </c>
-      <c r="E53" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>359</v>
-      </c>
-      <c r="G53" s="0" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="H53" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="I53" s="0" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="E54" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="E54" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="0" t="s">
+      <c r="G54" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="H54" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H54" s="0" t="s">
+      <c r="I54" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="I54" s="0" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="C55" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D55" s="0" t="s">
+      <c r="E55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E55" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="0" t="s">
+      <c r="G55" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="G55" s="0" t="s">
+      <c r="H55" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="H55" s="0" t="s">
+      <c r="I55" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I55" s="0" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="C56" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D56" s="0" t="s">
+      <c r="E56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E56" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="0" t="s">
+      <c r="G56" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="H56" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="H56" s="0" t="s">
+      <c r="I56" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I56" s="0" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="C57" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D57" s="0" t="s">
+      <c r="E57" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="0" t="s">
+      <c r="G57" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="H57" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="H57" s="0" t="s">
+      <c r="I57" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="I57" s="0" t="s">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="C58" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C58" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D58" s="0" t="s">
+      <c r="E58" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="E58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" s="0" t="s">
+      <c r="G58" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="H58" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="H58" s="0" t="s">
+      <c r="I58" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I58" s="0" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="C59" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D59" s="0" t="s">
+      <c r="E59" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E59" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="0" t="s">
+      <c r="G59" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="H59" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H59" s="0" t="s">
+      <c r="I59" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="I59" s="0" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="C60" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C60" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D60" s="0" t="s">
+      <c r="E60" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E60" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="0" t="s">
+      <c r="G60" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G60" s="0" t="s">
+      <c r="H60" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="H60" s="0" t="s">
+      <c r="I60" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="I60" s="0" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="C61" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C61" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D61" s="0" t="s">
+      <c r="E61" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E61" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" s="0" t="s">
+      <c r="G61" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="H61" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="H61" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="I61" s="0" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="C62" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C62" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D62" s="0" t="s">
+      <c r="E62" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E62" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" s="0" t="s">
+      <c r="G62" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="H62" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H62" s="0" t="s">
+      <c r="I62" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="I62" s="0" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="C63" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C63" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D63" s="0" t="s">
+      <c r="E63" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E63" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="0" t="s">
+      <c r="G63" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="G63" s="0" t="s">
+      <c r="H63" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="H63" s="0" t="s">
+      <c r="I63" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="I63" s="0" t="s">
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="C64" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C64" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D64" s="0" t="s">
+      <c r="E64" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="E64" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="0" t="s">
+      <c r="G64" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="G64" s="0" t="s">
+      <c r="H64" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="H64" s="0" t="s">
+      <c r="I64" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="I64" s="0" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="C65" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C65" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D65" s="0" t="s">
+      <c r="E65" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="E65" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F65" s="0" t="s">
+      <c r="G65" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="I65" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="I65" s="0" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="C66" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C66" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D66" s="0" t="s">
+      <c r="E66" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E66" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" s="0" t="s">
+      <c r="G66" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="I66" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="I66" s="0" t="s">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="C67" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C67" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D67" s="0" t="s">
+      <c r="E67" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="E67" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="0" t="s">
+      <c r="G67" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="I67" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I67" s="0" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="C68" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C68" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D68" s="0" t="s">
+      <c r="E68" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="E68" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" s="0" t="s">
+      <c r="G68" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="I68" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I68" s="0" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="C69" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C69" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D69" s="0" t="s">
+      <c r="E69" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="E69" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" s="0" t="s">
+      <c r="G69" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="I69" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="I69" s="0" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="C70" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C70" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D70" s="0" t="s">
+      <c r="E70" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E70" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F70" s="0" t="s">
+      <c r="G70" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="I70" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="I70" s="0" t="s">
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="C71" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C71" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D71" s="0" t="s">
+      <c r="E71" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="E71" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" s="0" t="s">
+      <c r="G71" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G71" s="0" t="s">
+      <c r="I71" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I71" s="0" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="C72" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C72" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D72" s="0" t="s">
+      <c r="E72" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="E72" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" s="0" t="s">
+      <c r="G72" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="I72" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="I72" s="0" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="C73" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C73" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D73" s="0" t="s">
+      <c r="E73" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E73" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" s="0" t="s">
+      <c r="G73" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="I73" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="I73" s="0" t="s">
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="C74" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C74" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D74" s="0" t="s">
+      <c r="E74" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E74" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" s="0" t="s">
+      <c r="G74" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="I74" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="I74" s="0" t="s">
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="C75" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C75" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D75" s="0" t="s">
+      <c r="E75" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="E75" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" s="0" t="s">
+      <c r="G75" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="I75" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="I75" s="0" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="C76" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C76" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D76" s="0" t="s">
+      <c r="E76" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E76" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" s="0" t="s">
+      <c r="G76" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="I76" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="I76" s="0" t="s">
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="C77" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D77" s="0" t="s">
+      <c r="E77" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E77" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" s="0" t="s">
+      <c r="G77" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="I77" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I77" s="0" t="s">
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="C78" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C78" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D78" s="0" t="s">
+      <c r="E78" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="E78" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" s="0" t="s">
+      <c r="G78" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="I78" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="I78" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="C79" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C79" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D79" s="0" t="s">
+      <c r="E79" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="E79" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F79" s="0" t="s">
+      <c r="G79" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="G79" s="0" t="s">
+      <c r="I79" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="I79" s="0" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="C80" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C80" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D80" s="0" t="s">
+      <c r="E80" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="E80" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F80" s="0" t="s">
+      <c r="G80" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="I80" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="I80" s="0" t="s">
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="C81" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C81" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D81" s="0" t="s">
+      <c r="E81" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E81" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" s="0" t="s">
+      <c r="G81" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="I81" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="I81" s="0" t="s">
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="C82" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D82" s="0" t="s">
+      <c r="E82" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E82" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F82" s="0" t="s">
+      <c r="G82" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="I82" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="I82" s="0" t="s">
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="C83" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D83" s="0" t="s">
+      <c r="E83" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="E83" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" s="0" t="s">
+      <c r="G83" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="I83" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="I83" s="0" t="s">
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="C84" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C84" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D84" s="0" t="s">
+      <c r="E84" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="E84" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" s="0" t="s">
+      <c r="G84" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="I84" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="I84" s="0" t="s">
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="C85" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C85" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D85" s="0" t="s">
+      <c r="E85" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="E85" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" s="0" t="s">
+      <c r="G85" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="G85" s="0" t="s">
+      <c r="I85" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="I85" s="0" t="s">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="B86" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="C86" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C86" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D86" s="0" t="s">
+      <c r="E86" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E86" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F86" s="0" t="s">
+      <c r="G86" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="I86" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="I86" s="0" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="B87" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="C87" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C87" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D87" s="0" t="s">
+      <c r="E87" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="E87" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" s="0" t="s">
+      <c r="G87" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="I87" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="I87" s="0" t="s">
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="B88" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="C88" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C88" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D88" s="0" t="s">
+      <c r="E88" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="E88" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F88" s="0" t="s">
+      <c r="G88" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="I88" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="I88" s="0" t="s">
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="B89" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="C89" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C89" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D89" s="0" t="s">
+      <c r="E89" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E89" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F89" s="0" t="s">
+      <c r="G89" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="I89" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="I89" s="0" t="s">
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="B90" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="C90" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C90" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D90" s="0" t="s">
+      <c r="E90" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E90" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F90" s="0" t="s">
+      <c r="G90" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="I90" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="I90" s="0" t="s">
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="B91" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="C91" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D91" s="0" t="s">
+      <c r="E91" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E91" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F91" s="0" t="s">
+      <c r="G91" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="G91" s="0" t="s">
+      <c r="I91" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="I91" s="0" t="s">
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="B92" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="C92" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C92" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D92" s="0" t="s">
+      <c r="E92" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="E92" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F92" s="0" t="s">
+      <c r="G92" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="G92" s="0" t="s">
+      <c r="I92" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="I92" s="0" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="B93" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="C93" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C93" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D93" s="0" t="s">
+      <c r="E93" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="E93" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" s="0" t="s">
+      <c r="G93" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="G93" s="0" t="s">
+      <c r="I93" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="I93" s="0" t="s">
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="B94" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="C94" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="C94" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D94" s="0" t="s">
+      <c r="E94" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="E94" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F94" s="0" t="s">
+      <c r="G94" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="G94" s="0" t="s">
+      <c r="I94" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="I94" s="0" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="B95" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="C95" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D95" s="0" t="s">
+      <c r="E95" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E95" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F95" s="0" t="s">
+      <c r="G95" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G95" s="0" t="s">
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="I95" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="B96" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="C96" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D96" s="0" t="s">
+      <c r="E96" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="E96" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" s="0" t="s">
+      <c r="G96" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G96" s="0" t="s">
+      <c r="I96" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="I96" s="0" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="C97" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="E97" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C97" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D97" s="0" t="s">
+      <c r="G97" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="E97" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F97" s="0" t="s">
+      <c r="H97" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="I97" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="H97" s="0" t="s">
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="I97" s="0" t="s">
+      <c r="B98" s="1" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="C98" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="E98" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D98" s="0" t="s">
+      <c r="G98" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E98" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" s="0" t="s">
+      <c r="H98" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="G98" s="0" t="s">
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="H98" s="0" t="s">
+      <c r="B99" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="I98" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="C99" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="E99" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C99" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D99" s="0" t="s">
+      <c r="G99" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E99" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F99" s="0" t="s">
+      <c r="H99" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="I99" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="H99" s="0" t="s">
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="I99" s="0" t="s">
+      <c r="B100" s="1" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="C100" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="E100" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D100" s="0" t="s">
+      <c r="G100" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="E100" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F100" s="0" t="s">
+      <c r="H100" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="I100" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="H100" s="0" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="I100" s="0" t="s">
+      <c r="B101" s="1" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="C101" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="E101" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C101" s="0" t="s">
-        <v>363</v>
-      </c>
-      <c r="D101" s="0" t="s">
+      <c r="G101" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E101" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F101" s="0" t="s">
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="C102" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="I101" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="D102" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="E102" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="C102" s="0" t="s">
+      <c r="G102" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="H102" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E102" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F102" s="0" t="s">
+      <c r="I102" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G102" s="0" t="s">
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="H102" s="0" t="s">
+      <c r="B103" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="I102" s="0" t="s">
+      <c r="C103" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="E103" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="G103" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C103" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D103" s="0" t="s">
+      <c r="H103" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="E103" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F103" s="0" t="s">
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="B104" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="H103" s="0" t="s">
+      <c r="C104" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="I103" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="E104" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="G104" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="C104" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D104" s="0" t="s">
+      <c r="H104" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="E104" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F104" s="0" t="s">
+      <c r="I104" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="G104" s="0" t="s">
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="H104" s="0" t="s">
+      <c r="B105" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="I104" s="0" t="s">
+      <c r="C105" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="E105" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="G105" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="C105" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D105" s="0" t="s">
+      <c r="H105" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="E105" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F105" s="0" t="s">
+      <c r="I105" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="B106" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="H105" s="0" t="s">
+      <c r="C106" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="I105" s="0" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="E106" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="G106" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="C106" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D106" s="0" t="s">
+      <c r="H106" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="E106" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F106" s="0" t="s">
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="H106" s="0" t="s">
+      <c r="C107" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="I106" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="E107" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="G107" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="C107" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D107" s="0" t="s">
+      <c r="H107" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E107" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F107" s="0" t="s">
+      <c r="B108" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="C108" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="H107" s="0" t="s">
-        <v>381</v>
-      </c>
-      <c r="I107" s="0" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="E108" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="G108" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C108" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D108" s="0" t="s">
+      <c r="H108" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="E108" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F108" s="0" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="B109" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="H108" s="0" t="s">
+      <c r="C109" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="I108" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="E109" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="G109" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C109" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D109" s="0" t="s">
+      <c r="I109" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="E109" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F109" s="0" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="B110" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="I109" s="0" t="s">
+      <c r="C110" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="E110" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="G110" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="C110" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D110" s="0" t="s">
+      <c r="I110" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="E110" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F110" s="0" t="s">
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="G110" s="0" t="s">
+      <c r="B111" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="I110" s="0" t="s">
+      <c r="C111" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="E111" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="G111" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C111" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D111" s="0" t="s">
+      <c r="I111" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="E111" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F111" s="0" t="s">
+      <c r="B112" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="C112" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="I111" s="0" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="E112" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="G112" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C112" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D112" s="0" t="s">
+      <c r="I112" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="E112" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F112" s="0" t="s">
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="B113" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="I112" s="0" t="s">
+      <c r="C113" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="E113" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="G113" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C113" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D113" s="0" t="s">
+      <c r="I113" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E113" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F113" s="0" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="B114" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="I113" s="0" t="s">
+      <c r="C114" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="E114" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="G114" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C114" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D114" s="0" t="s">
+      <c r="I114" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="E114" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F114" s="0" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="B115" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="I114" s="0" t="s">
+      <c r="C115" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="E115" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="G115" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="C115" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D115" s="0" t="s">
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="E115" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F115" s="0" t="s">
+      <c r="B116" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="C116" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="I115" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="E116" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="G116" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D116" s="0" t="s">
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="E116" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F116" s="0" t="s">
+      <c r="B117" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="C117" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="I116" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="E117" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="G117" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C117" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D117" s="0" t="s">
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="E117" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F117" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="C118" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="I117" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="E118" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="G118" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C118" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="D118" s="0" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="E118" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F118" s="0" t="s">
+      <c r="B119" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G118" s="0" t="s">
+      <c r="C119" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="I118" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="D119" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="E119" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C119" s="0" t="s">
+      <c r="G119" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="D119" s="0" t="s">
+      <c r="I119" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="E119" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F119" s="0" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="G119" s="0" t="s">
+      <c r="B120" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="I119" s="0" t="s">
+      <c r="C120" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="E120" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="G120" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C120" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D120" s="0" t="s">
+      <c r="I120" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="E120" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F120" s="0" t="s">
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="B121" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="I120" s="0" t="s">
+      <c r="C121" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="E121" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="G121" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="C121" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D121" s="0" t="s">
+      <c r="I121" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="E121" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F121" s="0" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="I121" s="0" t="s">
+      <c r="C122" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="E122" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="G122" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="C122" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D122" s="0" t="s">
+      <c r="I122" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="E122" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F122" s="0" t="s">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G122" s="0" t="s">
+      <c r="B123" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="I122" s="0" t="s">
+      <c r="C123" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="E123" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="G123" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D123" s="0" t="s">
+      <c r="I123" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="E123" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F123" s="0" t="s">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="B124" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="I123" s="0" t="s">
+      <c r="C124" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="E124" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="G124" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="C124" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D124" s="0" t="s">
+      <c r="I124" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E124" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F124" s="0" t="s">
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="B125" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="I124" s="0" t="s">
+      <c r="C125" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="E125" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="G125" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C125" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D125" s="0" t="s">
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="E125" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F125" s="0" t="s">
+      <c r="B126" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="C126" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="I125" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="E126" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="G126" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="C126" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D126" s="0" t="s">
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="E126" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F126" s="0" t="s">
+      <c r="B127" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="C127" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="I126" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="E127" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="G127" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="C127" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D127" s="0" t="s">
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="E127" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F127" s="0" t="s">
+      <c r="B128" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="C128" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="I127" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="E128" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="G128" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="C128" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D128" s="0" t="s">
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="E128" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F128" s="0" t="s">
+      <c r="B129" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="C129" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="I128" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="E129" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="G129" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="C129" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D129" s="0" t="s">
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="E129" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F129" s="0" t="s">
+      <c r="B130" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="G129" s="0" t="s">
+      <c r="C130" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="I129" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="E130" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="G130" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C130" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D130" s="0" t="s">
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="E130" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F130" s="0" t="s">
+      <c r="B131" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="C131" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="I130" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="E131" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="G131" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="C131" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D131" s="0" t="s">
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="E131" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F131" s="0" t="s">
+      <c r="B132" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="C132" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="I131" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="E132" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="G132" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="C132" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D132" s="0" t="s">
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="E132" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F132" s="0" t="s">
+      <c r="B133" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="C133" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="I132" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="E133" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="G133" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C133" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D133" s="0" t="s">
+      <c r="I133" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="E133" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F133" s="0" t="s">
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="B134" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="I133" s="0" t="s">
+      <c r="C134" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="E134" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="G134" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="C134" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D134" s="0" t="s">
+      <c r="I134" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="E134" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F134" s="0" t="s">
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="B135" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="I134" s="0" t="s">
+      <c r="C135" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="E135" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="G135" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="C135" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D135" s="0" t="s">
+      <c r="I135" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="E135" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F135" s="0" t="s">
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G135" s="0" t="s">
+      <c r="B136" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="I135" s="0" t="s">
+      <c r="C136" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="E136" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="G136" s="1" t="s">
         <v>852</v>
-      </c>
-      <c r="C136" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="D136" s="0" t="s">
-        <v>853</v>
-      </c>
-      <c r="E136" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F136" s="0" t="s">
-        <v>854</v>
-      </c>
-      <c r="G136" s="0" t="s">
-        <v>855</v>
-      </c>
-      <c r="I136" s="0" t="s">
-        <v>512</v>
       </c>
     </row>
   </sheetData>
